--- a/Inference_output/compare_models_metrics.xlsx
+++ b/Inference_output/compare_models_metrics.xlsx
@@ -545,40 +545,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9869713996280638</v>
+        <v>0.8970544243231916</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9897655804457796</v>
+        <v>0.9945350671803229</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7612600189844767</v>
+        <v>0.7307808961868286</v>
       </c>
       <c r="E3" t="n">
-        <v>0.91</v>
+        <v>0.03</v>
       </c>
       <c r="F3" t="n">
-        <v>0.71</v>
+        <v>0.6</v>
       </c>
       <c r="G3" t="n">
-        <v>0.98</v>
+        <v>0.52</v>
       </c>
       <c r="H3" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="I3" t="n">
-        <v>0.99</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01929361579733055</v>
+        <v>0.03225317078302397</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01978733973957527</v>
+        <v>0.01660965347294662</v>
       </c>
       <c r="M3" t="n">
-        <v>0.06311438999973867</v>
+        <v>0.07415241027214832</v>
       </c>
     </row>
     <row r="4">

--- a/Inference_output/compare_models_metrics.xlsx
+++ b/Inference_output/compare_models_metrics.xlsx
@@ -545,40 +545,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8970544243231916</v>
+        <v>0.9869713996280638</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9945350671803229</v>
+        <v>0.9897655804457796</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7307808961868286</v>
+        <v>0.7612600189844767</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03</v>
+        <v>0.91</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6</v>
+        <v>0.71</v>
       </c>
       <c r="G3" t="n">
-        <v>0.52</v>
+        <v>0.98</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="I3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J3" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="J3" t="n">
-        <v>0.92</v>
-      </c>
       <c r="K3" t="n">
-        <v>0.03225317078302397</v>
+        <v>0.01929361579733055</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01660965347294662</v>
+        <v>0.01978733973957527</v>
       </c>
       <c r="M3" t="n">
-        <v>0.07415241027214832</v>
+        <v>0.06311438999973867</v>
       </c>
     </row>
     <row r="4">
